--- a/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maëlys est au jardin avec papa. Des pommes sont dans un panier. Papa dit : on compte des objets. Maëlys touche. Un. Deux. Trois. Quatre. Cinq. Elle dit : cinq pommes. Papa en pose encore. Six. Sept. Huit. Neuf. Dix. Maëlys répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
+          <t>Maëlys est au jardin avec papa. Des pommes sont dans un panier. On compte des objets. Maëlys touche. Un. Deux. Trois. Quatre. Cinq. Cinq pommes. Papa en pose encore. Six. Sept. Huit. Neuf. Dix. Maëlys répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1285,6 +1301,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maëlys est au jardin avec papa. Des pommes sont dans un panier.
+papa|On compte des objets.
+narrateur|Maëlys touche. Un. Deux. Trois. Quatre. Cinq.
+narrateur|Cinq pommes. Papa en pose encore. Six. Sept. Huit. Neuf. Dix.
+narrateur|Maëlys répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1461,6 +1486,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maëlys touche les pommes. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1625,6 +1655,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maëlys a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1822,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le panier. Maëlys essuie ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1989,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2029,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1310,6 +1315,7 @@
 narrateur|Maëlys répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1499,7 @@
           <t>narrateur|Maëlys touche les pommes. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1660,6 +1667,7 @@
           <t>narrateur|Maëlys a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1835,7 @@
           <t>narrateur|Papa range le panier. Maëlys essuie ses mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1994,6 +2003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2012,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2046,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2261,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maëlys compte les pommes</t>
+          <t>Le panier mouillé de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'herbe mouillée colle aux bottes. Sarah trouve le panier sous le pommier, touche chaque pomme, dit le nombre. Papa en pose encore.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maëlys est au jardin avec papa. Des pommes sont dans un panier. On compte des objets. Maëlys touche. Un. Deux. Trois. Quatre. Cinq. Cinq pommes. Papa en pose encore. Six. Sept. Huit. Neuf. Dix. Maëlys répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
+          <t>L'herbe du jardin est encore mouillée. Une feuille collée au seau. Le pommier laisse tomber une goutte. La terre sent fort, toute douce. Les bottes de papa sont sombres. Un panier d'osier attend sous l'arbre. Un ver de terre glisse, tout lent. Le ciel est pâle, presque blanc. L'herbe colle un peu, Sarah. Tu as tes bottes ? Oui, papa. Elles sont froides. Je vous vois de la fenêtre. Le goûter arrive après. En ce moment, Sarah s'approche du panier. Dedans, des pommes luisantes. On va compter des objets, Sarah. Tu touches, et tu dis le nombre. Sarah pose un doigt sur une pomme. Un. La peau est lisse, un peu froide. Encore une. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq pommes. Bravo. Tu as dit le nombre. Papa en pose encore. Six. Sept. Huit. Neuf. Dix. Sarah répète. Dix. Tu as compté des objets. Dix pommes. C'est du bon travail, Sarah. Les petites ensemble ? Oui, maman. Les grosses ensemble. Sarah pousse les petites d'un côté. Une pomme roule, tout doucement. Elle fait un petit choc. C'est un son. Quel nom ? La pomme. Oui. Le nom du son, c'est la pomme. Tu as fini de compter ? Oui, papa. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1308,11 +1320,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maëlys est au jardin avec papa. Des pommes sont dans un panier.
-papa|On compte des objets.
-narrateur|Maëlys touche. Un. Deux. Trois. Quatre. Cinq.
-narrateur|Cinq pommes. Papa en pose encore. Six. Sept. Huit. Neuf. Dix.
-narrateur|Maëlys répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
+          <t>narrateur|L'herbe du jardin est encore mouillée.
+narrateur|Une feuille collée au seau.
+narrateur|Le pommier laisse tomber une goutte.
+narrateur|La terre sent fort, toute douce.
+narrateur|Les bottes de papa sont sombres.
+narrateur|Un panier d'osier attend sous l'arbre.
+narrateur|Un ver de terre glisse, tout lent.
+narrateur|Le ciel est pâle, presque blanc.
+papa|L'herbe colle un peu, Sarah.
+papa|Tu as tes bottes ?
+enfant-f|Oui, papa.
+enfant-f|Elles sont froides.
+maman|Je vous vois de la fenêtre.
+maman|Le goûter arrive après.
+narrateur|En ce moment, Sarah s'approche du panier.
+narrateur|Dedans, des pommes luisantes.
+papa|On va compter des objets, Sarah.
+papa|Tu touches, et tu dis le nombre.
+narrateur|Sarah pose un doigt sur une pomme.
+enfant-f|Un.
+narrateur|La peau est lisse, un peu froide.
+narrateur|Encore une.
+enfant-f|Deux.
+narrateur|Encore une.
+enfant-f|Trois.
+narrateur|Encore une.
+enfant-f|Quatre.
+narrateur|Encore une.
+enfant-f|Cinq.
+enfant-f|Cinq pommes.
+papa|Bravo.
+papa|Tu as dit le nombre.
+narrateur|Papa en pose encore.
+enfant-f|Six.
+enfant-f|Sept.
+enfant-f|Huit.
+enfant-f|Neuf.
+enfant-f|Dix.
+narrateur|Sarah répète.
+enfant-f|Dix.
+papa|Tu as compté des objets.
+papa|Dix pommes.
+papa|C'est du bon travail, Sarah.
+maman|Les petites ensemble ?
+enfant-f|Oui, maman.
+enfant-f|Les grosses ensemble.
+narrateur|Sarah pousse les petites d'un côté.
+narrateur|Une pomme roule, tout doucement.
+narrateur|Elle fait un petit choc.
+papa|C'est un son.
+papa|Quel nom ?
+enfant-f|La pomme.
+papa|Oui.
+papa|Le nom du son, c'est la pomme.
+papa|Tu as fini de compter ?
+enfant-f|Oui, papa.
+papa|Bravo, Sarah.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1340,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maëlys touche les pommes. Que fait-elle ?</t>
+          <t>Sarah touche les pommes. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1496,7 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maëlys touche les pommes. Que fait-elle ?</t>
+          <t>narrateur|Sarah touche les pommes.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1524,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maëlys a compté des objets. Elle a dit le nombre.</t>
+          <t>Sarah a compté des objets. Elle a dit le nombre. Dix pommes dans le panier. Bravo. C'est du bon travail, Sarah. Tu essuies tes mains ? Oui, maman. Sarah essuie ses mains sur l'herbe. L'herbe est froide et mouillée. Le panier est lourd, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1664,7 +1729,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maëlys a compté des objets. Elle a dit le nombre.</t>
+          <t>narrateur|Sarah a compté des objets.
+narrateur|Elle a dit le nombre.
+papa|Dix pommes dans le panier.
+papa|Bravo.
+maman|C'est du bon travail, Sarah.
+maman|Tu essuies tes mains ?
+enfant-f|Oui, maman.
+narrateur|Sarah essuie ses mains sur l'herbe.
+narrateur|L'herbe est froide et mouillée.
+papa|Le panier est lourd, maintenant.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1692,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le panier. Maëlys essuie ses mains.</t>
+          <t>Papa range le panier près de la porte. Une goutte tombe encore du pommier. On rentre, Sarah ? Oui. Le goûter est prêt. Ça sent la compote. J'ai compté des objets. Oui. Tu as dit le nombre. Sarah essuie ses mains. Les bottes laissent une petite trace.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1832,7 +1906,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le panier. Maëlys essuie ses mains.</t>
+          <t>narrateur|Papa range le panier près de la porte.
+narrateur|Une goutte tombe encore du pommier.
+papa|On rentre, Sarah ?
+enfant-f|Oui.
+maman|Le goûter est prêt.
+maman|Ça sent la compote.
+enfant-f|J'ai compté des objets.
+papa|Oui.
+papa|Tu as dit le nombre.
+narrateur|Sarah essuie ses mains.
+narrateur|Les bottes laissent une petite trace.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1860,7 +1944,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai touché les pommes. J'ai dit dix. Bravo, Sarah. Tu as fait du bon travail. Le panier repose près de la porte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2000,7 +2084,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai touché les pommes.
+enfant-f|J'ai dit dix.
+papa|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|Le panier repose près de la porte.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2022,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2060,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'herbe du jardin est encore mouillée. Une feuille collée au seau. Le pommier laisse tomber une goutte. La terre sent fort, toute douce. Les bottes de papa sont sombres. Un panier d'osier attend sous l'arbre. Un ver de terre glisse, tout lent. Le ciel est pâle, presque blanc. L'herbe colle un peu, Sarah. Tu as tes bottes ? Oui, papa. Elles sont froides. Je vous vois de la fenêtre. Le goûter arrive après. En ce moment, Sarah s'approche du panier. Dedans, des pommes luisantes. On va compter des objets, Sarah. Tu touches, et tu dis le nombre. Sarah pose un doigt sur une pomme. Un. La peau est lisse, un peu froide. Encore une. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq pommes. Bravo. Tu as dit le nombre. Papa en pose encore. Six. Sept. Huit. Neuf. Dix. Sarah répète. Dix. Tu as compté des objets. Dix pommes. C'est du bon travail, Sarah. Les petites ensemble ? Oui, maman. Les grosses ensemble. Sarah pousse les petites d'un côté. Une pomme roule, tout doucement. Elle fait un petit choc. C'est un son. Quel nom ? La pomme. Oui. Le nom du son, c'est la pomme. Tu as fini de compter ? Oui, papa. Bravo, Sarah.</t>
+          <t>L'herbe du jardin est encore mouillée. Une feuille collée au seau. Le pommier laisse tomber une goutte. La terre sent fort, toute douce. Les bottes de papa sont sombres. Un panier d'osier attend sous l'arbre. Un ver de terre glisse, tout lent. Le ciel est pâle, presque blanc. L'herbe colle un peu, Sarah. Tu as tes bottes ? Oui, papa. Elles sont froides. Je vous vois de la fenêtre. Le goûter arrive après. En ce moment, Sarah s'approche du panier. Dedans, des pommes luisantes. On va compter des objets, Sarah. Tu touches, et tu dis le nombre. Sarah pose un doigt sur une pomme. Un. La peau est lisse, un peu froide. Encore une. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq pommes. Bravo. Tu as dit le nombre. Papa en pose encore. Six. Sept. Huit. Neuf. Dix. Sarah répète. Dix. Tu as compté des objets. Dix pommes. Les petites ensemble ? Oui, maman. Les grosses ensemble. Sarah pousse les petites d'un côté. Une pomme roule, tout doucement. Elle fait un petit choc. C'est un son. Quel nom ? La pomme. Oui. Le nom du son, c'est la pomme. Tu as fini de compter ? Oui, papa. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maëlys est au jardin avec papa. Des pommes sont dans un panier. Papa dit : on compte des objets. Maëlys touche. Un. Deux. Trois. Quatre. Cinq. Elle dit : cinq pommes. Papa en pose encore. Six. Sept. Huit. Neuf. Dix. Maëlys répète : dix. Elle a compté des objets. Elle a dit le nombre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'herbe du jardin est encore mouillée. Une feuille collée au seau. Le pommier laisse tomber une goutte. La terre sent fort, toute douce. Les bottes de papa sont sombres. Un panier d'osier attend sous l'arbre. Un ver de terre glisse, tout lent. Le ciel est pâle, presque blanc. L'herbe colle un peu, Sarah. Tu as tes bottes ? Oui, papa. Elles sont froides. Je vous vois de la fenêtre. Le goûter arrive après. En ce moment, Sarah s'approche du panier. Dedans, des pommes luisantes. On va compter des objets, Sarah. Tu touches, et tu dis le nombre. Sarah pose un doigt sur une pomme. Un. La peau est lisse, un peu froide. Encore une. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq pommes. Bravo. Tu as dit le nombre. Papa en pose encore. Six. Sept. Huit. Neuf. Dix. Sarah répète. Dix. Tu as compté des objets. Dix pommes. Les petites ensemble ? Oui, maman. Les grosses ensemble. Sarah pousse les petites d'un côté. Une pomme roule, tout doucement. Elle fait un petit choc. C'est un son. Quel nom ? La pomme. Oui. Le nom du son, c'est la pomme. Tu as fini de compter ? Oui, papa. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1362,7 +1362,6 @@
 enfant-f|Dix.
 papa|Tu as compté des objets.
 papa|Dix pommes.
-papa|C'est du bon travail, Sarah.
 maman|Les petites ensemble ?
 enfant-f|Oui, maman.
 enfant-f|Les grosses ensemble.
@@ -1379,7 +1378,6 @@
 papa|Bravo, Sarah.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1409,7 +1407,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maëlys touche les pommes. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah touche les pommes. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1564,7 +1562,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1589,12 +1586,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a compté des objets. Elle a dit le nombre. Dix pommes dans le panier. Bravo. C'est du bon travail, Sarah. Tu essuies tes mains ? Oui, maman. Sarah essuie ses mains sur l'herbe. L'herbe est froide et mouillée. Le panier est lourd, maintenant.</t>
+          <t>Sarah a compté des objets. Elle a dit le nombre. Dix pommes dans le panier. Bravo. Tu essuies tes mains ? Oui, maman. Sarah essuie ses mains sur l'herbe. L'herbe est froide et mouillée. Le panier est lourd, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maëlys a compté des objets. Elle a dit le nombre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a compté des objets. Elle a dit le nombre. Dix pommes dans le panier. Bravo. Tu essuies tes mains ? Oui, maman. Sarah essuie ses mains sur l'herbe. L'herbe est froide et mouillée. Le panier est lourd, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1733,7 +1730,6 @@
 narrateur|Elle a dit le nombre.
 papa|Dix pommes dans le panier.
 papa|Bravo.
-maman|C'est du bon travail, Sarah.
 maman|Tu essuies tes mains ?
 enfant-f|Oui, maman.
 narrateur|Sarah essuie ses mains sur l'herbe.
@@ -1741,7 +1737,6 @@
 papa|Le panier est lourd, maintenant.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1771,7 +1766,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le panier. Maëlys essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le panier près de la porte. Une goutte tombe encore du pommier. On rentre, Sarah ? Oui. Le goûter est prêt. Ça sent la compote. J'ai compté des objets. Oui. Tu as dit le nombre. Sarah essuie ses mains. Les bottes laissent une petite trace.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1919,7 +1914,6 @@
 narrateur|Les bottes laissent une petite trace.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1944,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai touché les pommes. J'ai dit dix. Bravo, Sarah. Tu as fait du bon travail. Le panier repose près de la porte. L'histoire est finie.</t>
+          <t>J'ai touché les pommes. J'ai dit dix. Bravo, Sarah. Le panier repose près de la porte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai touché les pommes. J'ai dit dix. Bravo, Sarah. Le panier repose près de la porte.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2087,12 +2081,9 @@
           <t>enfant-f|J'ai touché les pommes.
 enfant-f|J'ai dit dix.
 papa|Bravo, Sarah.
-maman|Tu as fait du bon travail.
-narrateur|Le panier repose près de la porte.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le panier repose près de la porte.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2111,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2147,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maëlys, papa</t>
+          <t>Sarah, papa, maman</t>
         </is>
       </c>
     </row>
